--- a/data/tags/סינגלים חדשים/global/2026-04-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-04-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L16"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>בוצר &amp; עקיבא – אורחים לרגע</v>
+        <v>חג׳בי - כלה בלבן קאבר</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-23</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%91%d7%95%d7%a6%d7%a8-%d7%a2%d7%a7%d7%99%d7%91%d7%90-%d7%90%d7%95%d7%a8%d7%97%d7%99%d7%9d-%d7%9c%d7%a8%d7%92%d7%a2/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410601&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-23</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "אורחים לרגע” של אליעזר בוצר ועקיבא תורג'מן הוא יצירה טעונה מאוד, שנעה בין שבר עמוק לבין מבט מפויס על החיים והנצח. יש בו תחושה כמעט נבואית כאילו הוא מביט על החיים מלמעלה, בפרספקטיבה של זמניות. המשפט החוזר “אנחנו רק</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,544 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>בוצר &amp; עקיבא – אורחים לרגע</v>
+        <v>חג׳בי - כלה בלבן קאבר</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>אבי אילסון &amp; אהרל'ע סאמעט - המלמד תורה - גרסה ווקאלית</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410600&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>אבי אילסון &amp; אהרל'ע סאמעט - המלמד תורה - גרסה ווקאלית</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>שמוליק קליין - שתרגילנו - גרסה ווקאלית</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410599&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>שמוליק קליין - שתרגילנו - גרסה ווקאלית</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>שמוליק קליין - ניתאי הארבלי - גרסה ווקאלית</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410598&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>שמוליק קליין - ניתאי הארבלי - גרסה ווקאלית</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>שיראל חדד - יאללה תרקדו</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410597&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>שיראל חדד - יאללה תרקדו</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>פרחי ירושלים - מחרוזת עצמאות נולדתי לשלום &amp; כאן נולדתי 2026</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410596&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>פרחי ירושלים - מחרוזת עצמאות נולדתי לשלום &amp; כאן נולדתי 2026</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>פרחי ירושלים - ישראל שלי</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410595&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>פרחי ירושלים - ישראל שלי</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>עילאי פרץ - אהבה משולשת</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410594&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>עילאי פרץ - אהבה משולשת</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>מלכה בי &amp; דותנס - אני יכול</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410593&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>מלכה בי &amp; דותנס - אני יכול</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>חג'בי - להתאחד - גרסה ווקאלית</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410592&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>חג'בי - להתאחד - גרסה ווקאלית</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>אריאל קנדאבי &amp; מור דהרי - הותר לפרסום</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410591&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>אריאל קנדאבי &amp; מור דהרי - הותר לפרסום</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>אריאל קנדאבי - מצאתי מקום</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410590&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>אריאל קנדאבי - מצאתי מקום</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>אליאור נונה - מחרוזת שיכורים 2026</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410589&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>אליאור נונה - מחרוזת שיכורים 2026</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>איתיאל - מחרוזת דמעות 2026</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="C15" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410588&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v>איתיאל - מחרוזת דמעות 2026</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>אבנתא דליבא - האור הטוב הזה</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="C16" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410587&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
+      </c>
+      <c r="D16" t="str">
+        <v>2026-04-23</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v>אבנתא דליבא - האור הטוב הזה</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L16"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-04-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-04-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>חג׳בי - כלה בלבן קאבר</v>
+        <v>יובל גולד - בית במושב</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410601&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410610&amp;sid=11ff19e669c72ca7c585a951baadd9e7</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>חג׳בי - כלה בלבן קאבר</v>
+        <v>יובל גולד - בית במושב</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>אבי אילסון &amp; אהרל'ע סאמעט - המלמד תורה - גרסה ווקאלית</v>
+        <v>מיטב אמני ישראל - אשת חיל 2026</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410600&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410609&amp;sid=11ff19e669c72ca7c585a951baadd9e7</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>אבי אילסון &amp; אהרל'ע סאמעט - המלמד תורה - גרסה ווקאלית</v>
+        <v>מיטב אמני ישראל - אשת חיל 2026</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>שמוליק קליין - שתרגילנו - גרסה ווקאלית</v>
+        <v>נאור כהן - לא לבד</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410599&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410608&amp;sid=11ff19e669c72ca7c585a951baadd9e7</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>שמוליק קליין - שתרגילנו - גרסה ווקאלית</v>
+        <v>נאור כהן - לא לבד</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>שמוליק קליין - ניתאי הארבלי - גרסה ווקאלית</v>
+        <v>מורן לוי - מי אמור</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410598&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410607&amp;sid=11ff19e669c72ca7c585a951baadd9e7</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-04-23</v>
+        <v>2026-04-24</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,430 +583,12 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>שמוליק קליין - ניתאי הארבלי - גרסה ווקאלית</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>שיראל חדד - יאללה תרקדו</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410597&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>שיראל חדד - יאללה תרקדו</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>פרחי ירושלים - מחרוזת עצמאות נולדתי לשלום &amp; כאן נולדתי 2026</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410596&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>פרחי ירושלים - מחרוזת עצמאות נולדתי לשלום &amp; כאן נולדתי 2026</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>פרחי ירושלים - ישראל שלי</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410595&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>פרחי ירושלים - ישראל שלי</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>עילאי פרץ - אהבה משולשת</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410594&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>עילאי פרץ - אהבה משולשת</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>מלכה בי &amp; דותנס - אני יכול</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410593&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>מלכה בי &amp; דותנס - אני יכול</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>חג'בי - להתאחד - גרסה ווקאלית</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410592&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v>חג'בי - להתאחד - גרסה ווקאלית</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>אריאל קנדאבי &amp; מור דהרי - הותר לפרסום</v>
-      </c>
-      <c r="B12" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410591&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
-      </c>
-      <c r="D12" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="E12" t="str">
-        <v/>
-      </c>
-      <c r="F12" t="str">
-        <v/>
-      </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
-      <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J12" t="str">
-        <v/>
-      </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12" t="str">
-        <v>אריאל קנדאבי &amp; מור דהרי - הותר לפרסום</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>אריאל קנדאבי - מצאתי מקום</v>
-      </c>
-      <c r="B13" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="C13" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410590&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
-      </c>
-      <c r="D13" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="E13" t="str">
-        <v/>
-      </c>
-      <c r="F13" t="str">
-        <v/>
-      </c>
-      <c r="G13" t="str">
-        <v/>
-      </c>
-      <c r="H13" t="str">
-        <v/>
-      </c>
-      <c r="I13" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J13" t="str">
-        <v/>
-      </c>
-      <c r="K13" t="str">
-        <v/>
-      </c>
-      <c r="L13" t="str">
-        <v>אריאל קנדאבי - מצאתי מקום</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>אליאור נונה - מחרוזת שיכורים 2026</v>
-      </c>
-      <c r="B14" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="C14" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410589&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
-      </c>
-      <c r="D14" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="E14" t="str">
-        <v/>
-      </c>
-      <c r="F14" t="str">
-        <v/>
-      </c>
-      <c r="G14" t="str">
-        <v/>
-      </c>
-      <c r="H14" t="str">
-        <v/>
-      </c>
-      <c r="I14" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J14" t="str">
-        <v/>
-      </c>
-      <c r="K14" t="str">
-        <v/>
-      </c>
-      <c r="L14" t="str">
-        <v>אליאור נונה - מחרוזת שיכורים 2026</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>איתיאל - מחרוזת דמעות 2026</v>
-      </c>
-      <c r="B15" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="C15" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410588&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
-      </c>
-      <c r="D15" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="E15" t="str">
-        <v/>
-      </c>
-      <c r="F15" t="str">
-        <v/>
-      </c>
-      <c r="G15" t="str">
-        <v/>
-      </c>
-      <c r="H15" t="str">
-        <v/>
-      </c>
-      <c r="I15" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J15" t="str">
-        <v/>
-      </c>
-      <c r="K15" t="str">
-        <v/>
-      </c>
-      <c r="L15" t="str">
-        <v>איתיאל - מחרוזת דמעות 2026</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>אבנתא דליבא - האור הטוב הזה</v>
-      </c>
-      <c r="B16" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="C16" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410587&amp;sid=70fdb7173863b0c0d62bcf73bbd87464</v>
-      </c>
-      <c r="D16" t="str">
-        <v>2026-04-23</v>
-      </c>
-      <c r="E16" t="str">
-        <v/>
-      </c>
-      <c r="F16" t="str">
-        <v/>
-      </c>
-      <c r="G16" t="str">
-        <v/>
-      </c>
-      <c r="H16" t="str">
-        <v/>
-      </c>
-      <c r="I16" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J16" t="str">
-        <v/>
-      </c>
-      <c r="K16" t="str">
-        <v/>
-      </c>
-      <c r="L16" t="str">
-        <v>אבנתא דליבא - האור הטוב הזה</v>
+        <v>מורן לוי - מי אמור</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L16"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-04-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-04-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>יובל גולד - בית במושב</v>
+        <v>יובל גולד – בית במושב</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-24</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410610&amp;sid=11ff19e669c72ca7c585a951baadd9e7</v>
+        <v>https://yosmusic.com/%d7%99%d7%95%d7%91%d7%9c-%d7%92%d7%95%d7%9c%d7%93-%d7%91%d7%99%d7%aa-%d7%91%d7%9e%d7%95%d7%a9%d7%91/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-24</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>הטקסט של „"בית במושב” של יובל גולד עובד בדיוק על הקו שבין פשטות יומיומית לבין הצהרה רגשית עמוקה, בקצב שמשרת נרטיב אישי בבלדת רוק נוגה. השיר נשען על קצב יציב (כמעט “הליכה” רגועה), בלי שינויים דרמטיים: בינוני-איטי שיוצר תחושת אינטימיות</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,126 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>יובל גולד - בית במושב</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>מיטב אמני ישראל - אשת חיל 2026</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-04-24</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410609&amp;sid=11ff19e669c72ca7c585a951baadd9e7</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-04-24</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>מיטב אמני ישראל - אשת חיל 2026</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>נאור כהן - לא לבד</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-04-24</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410608&amp;sid=11ff19e669c72ca7c585a951baadd9e7</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-04-24</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>נאור כהן - לא לבד</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>מורן לוי - מי אמור</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-04-24</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410607&amp;sid=11ff19e669c72ca7c585a951baadd9e7</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-04-24</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>מורן לוי - מי אמור</v>
+        <v>יובל גולד – בית במושב</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-04-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-04-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>יובל גולד – בית במושב</v>
+        <v>תהילה - מה שאני</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-24</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%95%d7%91%d7%9c-%d7%92%d7%95%d7%9c%d7%93-%d7%91%d7%99%d7%aa-%d7%91%d7%9e%d7%95%d7%a9%d7%91/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410612&amp;sid=14abf7149976c01670080bda4e258547</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-24</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>הטקסט של „"בית במושב” של יובל גולד עובד בדיוק על הקו שבין פשטות יומיומית לבין הצהרה רגשית עמוקה, בקצב שמשרת נרטיב אישי בבלדת רוק נוגה. השיר נשען על קצב יציב (כמעט “הליכה” רגועה), בלי שינויים דרמטיים: בינוני-איטי שיוצר תחושת אינטימיות</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,50 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>יובל גולד – בית במושב</v>
+        <v>תהילה - מה שאני</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>ישראל מועלמי - אין יאוש בעולם כלל</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-04-24</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410611&amp;sid=14abf7149976c01670080bda4e258547</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-04-24</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>ישראל מועלמי - אין יאוש בעולם כלל</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-04-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-04-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>תהילה - מה שאני</v>
+        <v>ויולט – בסוף יגיע הבוקר</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-26</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410612&amp;sid=14abf7149976c01670080bda4e258547</v>
+        <v>https://yosmusic.com/%d7%95%d7%99%d7%95%d7%9c%d7%98-%d7%91%d7%a1%d7%95%d7%a3-%d7%99%d7%92%d7%99%d7%a2-%d7%94%d7%91%d7%95%d7%a7%d7%a8/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-24</v>
+        <v>2026-04-26</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>"בסוף יגיע הבוקר” של ויולט לוקץ' הוא שיר של אופטימיות, כזו שמודעת לכך שלחושך יש נוכחות, רק לא נצח. המשפט: “בסוף יגיע הבוקר” לא רק מבטיח תקווה אלא מנסח תפיסת עולם: מצבים קשים הם זמניים, גם כשאין שליטה (“לא משנה</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,50 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>תהילה - מה שאני</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>ישראל מועלמי - אין יאוש בעולם כלל</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-04-24</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410611&amp;sid=14abf7149976c01670080bda4e258547</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-04-24</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>ישראל מועלמי - אין יאוש בעולם כלל</v>
+        <v>ויולט – בסוף יגיע הבוקר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-04-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-04-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L5"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ויולט – בסוף יגיע הבוקר</v>
+        <v>אמיר חיים - את כל רגע משתנה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-26</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%95%d7%99%d7%95%d7%9c%d7%98-%d7%91%d7%a1%d7%95%d7%a3-%d7%99%d7%92%d7%99%d7%a2-%d7%94%d7%91%d7%95%d7%a7%d7%a8/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410618&amp;sid=e1a9ede86a9fca5d6ec26ec06669b772</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-26</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>"בסוף יגיע הבוקר” של ויולט לוקץ' הוא שיר של אופטימיות, כזו שמודעת לכך שלחושך יש נוכחות, רק לא נצח. המשפט: “בסוף יגיע הבוקר” לא רק מבטיח תקווה אלא מנסח תפיסת עולם: מצבים קשים הם זמניים, גם כשאין שליטה (“לא משנה</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,126 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ויולט – בסוף יגיע הבוקר</v>
+        <v>אמיר חיים - את כל רגע משתנה</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>אורן כהן - בסוף הכל נגמר</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-04-26</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410617&amp;sid=e1a9ede86a9fca5d6ec26ec06669b772</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-04-26</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>אורן כהן - בסוף הכל נגמר</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>אבנר הררי - הזאב האחרון</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-04-26</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410616&amp;sid=e1a9ede86a9fca5d6ec26ec06669b772</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-04-26</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>אבנר הררי - הזאב האחרון</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>אביגיל - אני רק ילדה</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-04-26</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410615&amp;sid=e1a9ede86a9fca5d6ec26ec06669b772</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-04-26</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>אביגיל - אני רק ילדה</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-04-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-04-week04/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אמיר חיים - את כל רגע משתנה</v>
+        <v>ויולט - בסוף יגיע הבוקר</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-26</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410618&amp;sid=e1a9ede86a9fca5d6ec26ec06669b772</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410621&amp;sid=8b656ce0fba7900fe3dab49fd65a8d94</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-26</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אמיר חיים - את כל רגע משתנה</v>
+        <v>ויולט - בסוף יגיע הבוקר</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>אורן כהן - בסוף הכל נגמר</v>
+        <v>היוצר האלמוני - איך ממשיכים מכאן</v>
       </c>
       <c r="B3" t="str">
         <v>2026-04-26</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410617&amp;sid=e1a9ede86a9fca5d6ec26ec06669b772</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410620&amp;sid=8b656ce0fba7900fe3dab49fd65a8d94</v>
       </c>
       <c r="D3" t="str">
         <v>2026-04-26</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>אורן כהן - בסוף הכל נגמר</v>
+        <v>היוצר האלמוני - איך ממשיכים מכאן</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>אבנר הררי - הזאב האחרון</v>
+        <v>אסאלה - אהבה לחיילים</v>
       </c>
       <c r="B4" t="str">
         <v>2026-04-26</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410616&amp;sid=e1a9ede86a9fca5d6ec26ec06669b772</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410619&amp;sid=8b656ce0fba7900fe3dab49fd65a8d94</v>
       </c>
       <c r="D4" t="str">
         <v>2026-04-26</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>אבנר הררי - הזאב האחרון</v>
+        <v>אסאלה - אהבה לחיילים</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>אביגיל - אני רק ילדה</v>
+        <v>איציק איזמירלי – לא אמרת</v>
       </c>
       <c r="B5" t="str">
         <v>2026-04-26</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410615&amp;sid=e1a9ede86a9fca5d6ec26ec06669b772</v>
+        <v>https://yosmusic.com/%d7%90%d7%99%d7%a6%d7%99%d7%a7-%d7%90%d7%99%d7%96%d7%9e%d7%99%d7%a8%d7%9c%d7%99-%d7%9c%d7%90-%d7%90%d7%9e%d7%a8%d7%aa/</v>
       </c>
       <c r="D5" t="str">
         <v>2026-04-26</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>איציק איזמירלי מקונן אהבה נכזבת בבלדה דרמטית שממקמת את עצמה עמוק בז’אנר של שירי שברון לב קלאסיים, בשפה ישירה מאוד וטון של זעקה לא מעובדת. כבר מהשורה – “מכל הנשים בעולם אהבתי רק אותך” נבנית תפיסה של אהבה בלעדית, טוטאלית,</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -583,7 +583,7 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>אביגיל - אני רק ילדה</v>
+        <v>איציק איזמירלי – לא אמרת</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-04-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-04-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ויולט - בסוף יגיע הבוקר</v>
+        <v>שקד אבידר - רגע לנשום</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-26</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410621&amp;sid=8b656ce0fba7900fe3dab49fd65a8d94</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410626&amp;sid=e159f64b57b6881a30ca5f987717e153</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-26</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ויולט - בסוף יגיע הבוקר</v>
+        <v>שקד אבידר - רגע לנשום</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>היוצר האלמוני - איך ממשיכים מכאן</v>
+        <v>שי וינר - יבוא שלום - גרסה ווקאלית</v>
       </c>
       <c r="B3" t="str">
         <v>2026-04-26</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410620&amp;sid=8b656ce0fba7900fe3dab49fd65a8d94</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410625&amp;sid=e159f64b57b6881a30ca5f987717e153</v>
       </c>
       <c r="D3" t="str">
         <v>2026-04-26</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>היוצר האלמוני - איך ממשיכים מכאן</v>
+        <v>שי וינר - יבוא שלום - גרסה ווקאלית</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>אסאלה - אהבה לחיילים</v>
+        <v>מלי יקותיאל - אדע לאהוב</v>
       </c>
       <c r="B4" t="str">
         <v>2026-04-26</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410619&amp;sid=8b656ce0fba7900fe3dab49fd65a8d94</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410624&amp;sid=e159f64b57b6881a30ca5f987717e153</v>
       </c>
       <c r="D4" t="str">
         <v>2026-04-26</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>אסאלה - אהבה לחיילים</v>
+        <v>מלי יקותיאל - אדע לאהוב</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>איציק איזמירלי – לא אמרת</v>
+        <v>מאור גוילי - שורף אדומים</v>
       </c>
       <c r="B5" t="str">
         <v>2026-04-26</v>
       </c>
       <c r="C5" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%99%d7%a6%d7%99%d7%a7-%d7%90%d7%99%d7%96%d7%9e%d7%99%d7%a8%d7%9c%d7%99-%d7%9c%d7%90-%d7%90%d7%9e%d7%a8%d7%aa/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410623&amp;sid=e159f64b57b6881a30ca5f987717e153</v>
       </c>
       <c r="D5" t="str">
         <v>2026-04-26</v>
@@ -565,7 +565,7 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>איציק איזמירלי מקונן אהבה נכזבת בבלדה דרמטית שממקמת את עצמה עמוק בז’אנר של שירי שברון לב קלאסיים, בשפה ישירה מאוד וטון של זעקה לא מעובדת. כבר מהשורה – “מכל הנשים בעולם אהבתי רק אותך” נבנית תפיסה של אהבה בלעדית, טוטאלית,</v>
+        <v/>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -583,12 +583,50 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>איציק איזמירלי – לא אמרת</v>
+        <v>מאור גוילי - שורף אדומים</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>יוסף עבאדי - רגעים של אושר - גרסה ווקאלית</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-04-26</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410622&amp;sid=e159f64b57b6881a30ca5f987717e153</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-04-26</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>יוסף עבאדי - רגעים של אושר - גרסה ווקאלית</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-04-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-04-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L6"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שקד אבידר - רגע לנשום</v>
+        <v>יערה טופ – רק את</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410626&amp;sid=e159f64b57b6881a30ca5f987717e153</v>
+        <v>https://yosmusic.com/%d7%99%d7%a2%d7%a8%d7%94-%d7%98%d7%95%d7%a4-%d7%a8%d7%a7-%d7%90%d7%aa/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-26</v>
+        <v>2026-04-27</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>השיר "רק את” של יערה טופ הוא טקסט טעון שמצליח ללכוד רגע מאוד ספציפי אחרי פרידה: הרגע שבו הצד שעזב חוזר לא מאהבה מחודשת, אלא מתוך חולשה, בדידות או חרטה. הדוברת מציבה גבול ברור, ובכך הופכת את השיר לא רק</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,164 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שקד אבידר - רגע לנשום</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>שי וינר - יבוא שלום - גרסה ווקאלית</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-04-26</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410625&amp;sid=e159f64b57b6881a30ca5f987717e153</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-04-26</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>שי וינר - יבוא שלום - גרסה ווקאלית</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>מלי יקותיאל - אדע לאהוב</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-04-26</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410624&amp;sid=e159f64b57b6881a30ca5f987717e153</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-04-26</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>מלי יקותיאל - אדע לאהוב</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>מאור גוילי - שורף אדומים</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-04-26</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410623&amp;sid=e159f64b57b6881a30ca5f987717e153</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-04-26</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>מאור גוילי - שורף אדומים</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>יוסף עבאדי - רגעים של אושר - גרסה ווקאלית</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-04-26</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410622&amp;sid=e159f64b57b6881a30ca5f987717e153</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-04-26</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>יוסף עבאדי - רגעים של אושר - גרסה ווקאלית</v>
+        <v>יערה טופ – רק את</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-04-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-04-week04/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>יערה טופ – רק את</v>
+        <v>אברהם טל מוש בן ארי – מה אם הייתי</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-27</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%a2%d7%a8%d7%94-%d7%98%d7%95%d7%a4-%d7%a8%d7%a7-%d7%90%d7%aa/</v>
+        <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%9e%d7%95%d7%a9-%d7%91%d7%9f-%d7%90%d7%a8%d7%99-%d7%9e%d7%94-%d7%90%d7%9d-%d7%94%d7%99%d7%99%d7%aa%d7%99/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-27</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "רק את” של יערה טופ הוא טקסט טעון שמצליח ללכוד רגע מאוד ספציפי אחרי פרידה: הרגע שבו הצד שעזב חוזר לא מאהבה מחודשת, אלא מתוך חולשה, בדידות או חרטה. הדוברת מציבה גבול ברור, ובכך הופכת את השיר לא רק</v>
+        <v>"מה אם הייתי” בביצוע הדואט של מוש בן ארי ואברהם טל מציג גישה שונה מאוד לשאלת העבר והחרטה: במקום התחשבנות כואבת, יש כאן השלמה, קלילות ואפילו חגיגה של מה שהיה. על פניו, השיר בנוי סביב שאלה קלאסית – "מה אם</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>יערה טופ – רק את</v>
+        <v>אברהם טל מוש בן ארי – מה אם הייתי</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-04-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-04-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אברהם טל מוש בן ארי – מה אם הייתי</v>
+        <v>יאיר רינגר &amp; שיר רינגר - מזיז את הגוף</v>
       </c>
       <c r="B2" t="str">
         <v>2026-04-27</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%91%d7%a8%d7%94%d7%9d-%d7%98%d7%9c-%d7%9e%d7%95%d7%a9-%d7%91%d7%9f-%d7%90%d7%a8%d7%99-%d7%9e%d7%94-%d7%90%d7%9d-%d7%94%d7%99%d7%99%d7%aa%d7%99/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410634&amp;sid=12a34684e5cb739ab2908d174e7f023e</v>
       </c>
       <c r="D2" t="str">
         <v>2026-04-27</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>"מה אם הייתי” בביצוע הדואט של מוש בן ארי ואברהם טל מציג גישה שונה מאוד לשאלת העבר והחרטה: במקום התחשבנות כואבת, יש כאן השלמה, קלילות ואפילו חגיגה של מה שהיה. על פניו, השיר בנוי סביב שאלה קלאסית – "מה אם</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,202 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אברהם טל מוש בן ארי – מה אם הייתי</v>
+        <v>יאיר רינגר &amp; שיר רינגר - מזיז את הגוף</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>תומר קינן - חלום במציאות</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410633&amp;sid=12a34684e5cb739ab2908d174e7f023e</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>תומר קינן - חלום במציאות</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>שלומי ימין - אוהב אותך</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410632&amp;sid=12a34684e5cb739ab2908d174e7f023e</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>שלומי ימין - אוהב אותך</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>שיראל חדד - אמא שלה</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410631&amp;sid=12a34684e5cb739ab2908d174e7f023e</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>שיראל חדד - אמא שלה</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>אניס נקש - בליבי</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410629&amp;sid=12a34684e5cb739ab2908d174e7f023e</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>אניס נקש - בליבי</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>אברהם טל &amp; מוש בן ארי - מה אם הייתי</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410628&amp;sid=12a34684e5cb739ab2908d174e7f023e</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-04-27</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>אברהם טל &amp; מוש בן ארי - מה אם הייתי</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-04-week04/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-04-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>יאיר רינגר &amp; שיר רינגר - מזיז את הגוף</v>
+        <v>כברה קסאי – שמש באה בזמן</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410634&amp;sid=12a34684e5cb739ab2908d174e7f023e</v>
+        <v>https://yosmusic.com/%d7%9b%d7%91%d7%a8%d7%94-%d7%a7%d7%a1%d7%90%d7%99-%d7%a9%d7%9e%d7%a9-%d7%91%d7%90%d7%94-%d7%91%d7%96%d7%9e%d7%9f/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-04-27</v>
+        <v>2026-04-28</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>השיר "ושמש באה בזמן” של כברה קסאי הוא שיר אינטימי ועדין שמצליח להישמע כמו תפילה אישית, ובו בזמן לגעת בפחד אוניברסלי: דאגה לאדם קרוב שנמצא רחוק, בסכנה. לב השיר נמצא במתח בין שני כוחות: חרדה וחוסר שליטה ("בלילות קשה…”, „קולות</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,202 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>יאיר רינגר &amp; שיר רינגר - מזיז את הגוף</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>תומר קינן - חלום במציאות</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-04-27</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410633&amp;sid=12a34684e5cb739ab2908d174e7f023e</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-04-27</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>תומר קינן - חלום במציאות</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>שלומי ימין - אוהב אותך</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-04-27</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410632&amp;sid=12a34684e5cb739ab2908d174e7f023e</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-04-27</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>שלומי ימין - אוהב אותך</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>שיראל חדד - אמא שלה</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-04-27</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410631&amp;sid=12a34684e5cb739ab2908d174e7f023e</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-04-27</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>שיראל חדד - אמא שלה</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>אניס נקש - בליבי</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-04-27</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410629&amp;sid=12a34684e5cb739ab2908d174e7f023e</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-04-27</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>אניס נקש - בליבי</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>אברהם טל &amp; מוש בן ארי - מה אם הייתי</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-04-27</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=410628&amp;sid=12a34684e5cb739ab2908d174e7f023e</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-04-27</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>אברהם טל &amp; מוש בן ארי - מה אם הייתי</v>
+        <v>כברה קסאי – שמש באה בזמן</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L7"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>